--- a/tests/fixtures/catalogue/aemps-cima-sample.xlsx
+++ b/tests/fixtures/catalogue/aemps-cima-sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O143"/>
+  <dimension ref="A1:O146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6251,22 +6251,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1231791001</t>
+          <t>1231775001</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IBUPROFENO GEN.ORPH 5 MG/ML SOLUCION INYECTABLE EFG</t>
+          <t>REZZAYO 200 MG POLVO PARA CONCENTRADO PARA SOLUCION PARA PERFUSION</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Gen.Orph S.A.S.</t>
+          <t>Mundipharma Gmbh</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>05/07/2024</t>
+          <t>25/01/2024</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -6276,17 +6276,17 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>06/07/2024</t>
+          <t>26/01/2024</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>C01EB16</t>
+          <t>J02AX08</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>IBUPROFENO</t>
+          <t>REZAFUNGINA, ACETATO DE</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -6299,12 +6299,17 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>Uso Hospitalario</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Biológicos</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6321,22 +6326,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>12680</t>
+          <t>1231791001</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ASPIRINA PLUS 500 mg/ 50 mg COMPRIMIDOS</t>
+          <t>IBUPROFENO GEN.ORPH 5 MG/ML SOLUCION INYECTABLE EFG</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bayer Hispania S.L.</t>
+          <t>Gen.Orph S.A.S.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>01/10/1949</t>
+          <t>05/07/2024</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -6346,21 +6351,21 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>01/10/1949</t>
+          <t>06/07/2024</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>N02BA51</t>
+          <t>C01EB16</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>CAFEINA, ACETILSALICILICO ACIDO</t>
+          <t>IBUPROFENO</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -6374,7 +6379,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Sin Receta</t>
+          <t>Uso Hospitalario</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6391,50 +6396,50 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>12680</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ASPIRINA COMPRIMIDOS</t>
+          <t>ASPIRINA PLUS 500 mg/ 50 mg COMPRIMIDOS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bayer Hellas A.E.</t>
+          <t>Bayer Hispania S.L.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>06/04/2010</t>
+          <t>01/10/1949</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Anulado</t>
+          <t>Autorizado</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>21/09/2023</t>
+          <t>01/10/1949</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>N02BA01</t>
+          <t>N02BA51</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>ACETILSALICILICO ACIDO</t>
+          <t>CAFEINA, ACETILSALICILICO ACIDO</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6461,46 +6466,46 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20000836IP1</t>
+          <t>13738</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ASPIRINA C 400 MG/240 MG COMPRIMIDOS EFERVESCENTES</t>
+          <t>ASPIRINA COMPRIMIDOS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bayer Bulgaria Eood</t>
+          <t>Bayer Hellas A.E.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>06/04/2010</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Autorizado</t>
+          <t>Anulado</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>21/09/2023</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>N02BA51</t>
+          <t>N02BA01</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>ACETILSALICILICO ACIDO, ASCORBICO ACIDO</t>
+          <t>ACETILSALICILICO ACIDO</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -6531,46 +6536,46 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>34491</t>
+          <t>20000836IP1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>POMADA BELLADONA ORRAVAN POMADA</t>
+          <t>ASPIRINA C 400 MG/240 MG COMPRIMIDOS EFERVESCENTES</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Laboratorio Reig Jofre, S.A.</t>
+          <t>Bayer Bulgaria Eood</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>01/09/1960</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Anulado</t>
+          <t>Autorizado</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>D04AX</t>
+          <t>N02BA51</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>BELLADONA EXTO BLANDO</t>
+          <t>ACETILSALICILICO ACIDO, ASCORBICO ACIDO</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -6601,22 +6606,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>36558</t>
+          <t>34491</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PRIMOBOLAN DEPOT 100 MG SOLUCION INYECTABLE</t>
+          <t>POMADA BELLADONA ORRAVAN POMADA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bayer Hispania S.L.</t>
+          <t>Laboratorio Reig Jofre, S.A.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>01/09/1961</t>
+          <t>01/09/1960</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6626,17 +6631,17 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>A14AA04</t>
+          <t>D04AX</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>METENOLONA ENANTATO</t>
+          <t>BELLADONA EXTO BLANDO</t>
         </is>
       </c>
       <c r="I88" t="n">
@@ -6654,7 +6659,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica</t>
+          <t>Sin Receta</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6671,42 +6676,42 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>37472</t>
+          <t>36558</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MORFINA SERRA 20 MG/ML SOLUCION INYECTABLE</t>
+          <t>PRIMOBOLAN DEPOT 100 MG SOLUCION INYECTABLE</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Laboratorios Serra Pamies S.A.U.</t>
+          <t>Bayer Hispania S.L.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>01/03/1962</t>
+          <t>01/09/1961</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Autorizado</t>
+          <t>Anulado</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>01/03/1962</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>N02AA01</t>
+          <t>A14AA04</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>MORFINA HIDROCLORURO TRIHIDRATO</t>
+          <t>METENOLONA ENANTATO</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -6714,7 +6719,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6724,12 +6729,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica. Estupefacientes</t>
+          <t>Medicamento Sujeto A Prescripción Médica</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -6741,50 +6746,50 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>40625</t>
+          <t>37472</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CALCIUMOSTEO 500 mg COMPRIMIDOS EFERVESCENTES</t>
+          <t>MORFINA SERRA 20 MG/ML SOLUCION INYECTABLE</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Haleon Spain S.A.</t>
+          <t>Laboratorios Serra Pamies S.A.U.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>01/03/1965</t>
+          <t>01/03/1962</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Suspenso</t>
+          <t>Autorizado</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>26/08/2022</t>
+          <t>01/03/1962</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>A12AX</t>
+          <t>N02AA01</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>CALCIO CARBONATO, LACTOGLUCONATO CALCIO</t>
+          <t>MORFINA HIDROCLORURO TRIHIDRATO</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6794,12 +6799,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Sin Receta</t>
+          <t>Medicamento Sujeto A Prescripción Médica. Estupefacientes</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -6811,50 +6816,50 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>42304</t>
+          <t>40625</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NOLOTIL 0,4 g/ml SOLUCION INYECTABLE Y PARA PERFUSION</t>
+          <t>CALCIUMOSTEO 500 mg COMPRIMIDOS EFERVESCENTES</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim Espana S.A.</t>
+          <t>Haleon Spain S.A.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>01/01/1966</t>
+          <t>01/03/1965</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Autorizado</t>
+          <t>Suspenso</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>01/01/1966</t>
+          <t>26/08/2022</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>N02BB02</t>
+          <t>A12AX</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>METAMIZOL MAGNESICO</t>
+          <t>CALCIO CARBONATO, LACTOGLUCONATO CALCIO</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6864,12 +6869,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica</t>
+          <t>Sin Receta</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -6881,22 +6886,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>42592</t>
+          <t>42304</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MORFINA B. BRAUN 20 mg/ml SOLUCION INYECTABLE</t>
+          <t>NOLOTIL 0,4 g/ml SOLUCION INYECTABLE Y PARA PERFUSION</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B Braun Medical S.A.</t>
+          <t>Boehringer Ingelheim Espana S.A.</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>01/06/1966</t>
+          <t>01/01/1966</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6906,17 +6911,17 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>01/06/1966</t>
+          <t>01/01/1966</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>N02AA01</t>
+          <t>N02BB02</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>MORFINA HIDROCLORURO TRIHIDRATO</t>
+          <t>METAMIZOL MAGNESICO</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -6934,7 +6939,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica. Estupefacientes</t>
+          <t>Medicamento Sujeto A Prescripción Médica</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6951,50 +6956,50 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>42972</t>
+          <t>42592</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Epistaxol solución cutánea</t>
+          <t>MORFINA B. BRAUN 20 mg/ml SOLUCION INYECTABLE</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Medical S.A.</t>
+          <t>B Braun Medical S.A.</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>01/04/1966</t>
+          <t>01/06/1966</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Suspenso</t>
+          <t>Autorizado</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>05/08/2025</t>
+          <t>01/06/1966</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>B02BC30</t>
+          <t>N02AA01</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>FENAZONA, RUTOSIDO, NAFAZOLINA HIDROCLORURO, EPINEFRINA</t>
+          <t>MORFINA HIDROCLORURO TRIHIDRATO</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -7004,12 +7009,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Sin Receta</t>
+          <t>Medicamento Sujeto A Prescripción Médica. Estupefacientes</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7021,50 +7026,50 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>43990</t>
+          <t>42972</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TERMALGIN 650 mg COMPRIMIDOS</t>
+          <t>Epistaxol solución cutánea</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Haleon Spain S.A.</t>
+          <t>Medical S.A.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>01/02/1967</t>
+          <t>01/04/1966</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Autorizado</t>
+          <t>Suspenso</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>01/02/1967</t>
+          <t>05/08/2025</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>N02BE01</t>
+          <t>B02BC30</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>PARACETAMOL</t>
+          <t>FENAZONA, RUTOSIDO, NAFAZOLINA HIDROCLORURO, EPINEFRINA</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -7091,22 +7096,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>47633</t>
+          <t>43990</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NOLOTIL 575 mg CAPSULAS DURAS</t>
+          <t>TERMALGIN 650 mg COMPRIMIDOS</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim Espana S.A.</t>
+          <t>Haleon Spain S.A.</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>01/03/1969</t>
+          <t>01/02/1967</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7116,17 +7121,17 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>01/03/1969</t>
+          <t>01/02/1967</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>N02BB02</t>
+          <t>N02BE01</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>METAMIZOL MAGNESICO</t>
+          <t>PARACETAMOL</t>
         </is>
       </c>
       <c r="I95" t="n">
@@ -7144,12 +7149,12 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica</t>
+          <t>Sin Receta</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -7161,22 +7166,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>52010</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GELOCATIL 650 mg COMPRIMIDOS</t>
+          <t>NOLOTIL 575 mg CAPSULAS DURAS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Vemedia Pharma Hispania S.A.</t>
+          <t>Boehringer Ingelheim Espana S.A.</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>01/01/1974</t>
+          <t>01/03/1969</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7186,17 +7191,17 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>01/01/1974</t>
+          <t>01/03/1969</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>N02BE01</t>
+          <t>N02BB02</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>PARACETAMOL</t>
+          <t>METAMIZOL MAGNESICO</t>
         </is>
       </c>
       <c r="I96" t="n">
@@ -7214,12 +7219,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Sin Receta</t>
+          <t>Medicamento Sujeto A Prescripción Médica</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -7231,22 +7236,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>52371</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AMOXICILINA ARDINE 500 mg POLVO PARA SUSPENSION ORAL EN SOBRES EFG</t>
+          <t>GELOCATIL 650 mg COMPRIMIDOS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Laboratorio Reig Jofre, S.A.</t>
+          <t>Vemedia Pharma Hispania S.A.</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>01/05/1974</t>
+          <t>01/01/1974</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -7256,17 +7261,17 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>01/05/1974</t>
+          <t>01/01/1974</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>J01CA04</t>
+          <t>N02BE01</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>AMOXICILINA TRIHIDRATO</t>
+          <t>PARACETAMOL</t>
         </is>
       </c>
       <c r="I97" t="n">
@@ -7284,7 +7289,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica</t>
+          <t>Sin Receta</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7301,42 +7306,42 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>55626</t>
+          <t>52371</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ENISON 5 MG POLVO PARA SOLUCIoN INYECTABLE</t>
+          <t>AMOXICILINA ARDINE 500 mg POLVO PARA SUSPENSION ORAL EN SOBRES EFG</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Laboratorio Stada S.L.</t>
+          <t>Laboratorio Reig Jofre, S.A.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>01/09/1981</t>
+          <t>01/05/1974</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Suspenso</t>
+          <t>Autorizado</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>04/12/2024</t>
+          <t>01/05/1974</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>L01CA03</t>
+          <t>J01CA04</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>VINDESINA SULFATO</t>
+          <t>AMOXICILINA TRIHIDRATO</t>
         </is>
       </c>
       <c r="I98" t="n">
@@ -7344,7 +7349,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7354,12 +7359,12 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Uso Hospitalario</t>
+          <t>Medicamento Sujeto A Prescripción Médica</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -7371,42 +7376,42 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>57899</t>
+          <t>55626</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MST CONTINUS 60 mg COMPRIMIDOS DE LIBERACION PROLONGADA</t>
+          <t>ENISON 5 MG POLVO PARA SOLUCIoN INYECTABLE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Mundipharma Pharmaceuticals S.L.</t>
+          <t>Laboratorio Stada S.L.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>01/09/1988</t>
+          <t>01/09/1981</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Autorizado</t>
+          <t>Suspenso</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>01/09/1988</t>
+          <t>04/12/2024</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>N02AA01</t>
+          <t>L01CA03</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>MORFINA SULFATO</t>
+          <t>VINDESINA SULFATO</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -7414,7 +7419,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7424,7 +7429,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica. Estupefacientes</t>
+          <t>Uso Hospitalario</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7441,12 +7446,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>57900</t>
+          <t>57899</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MST CONTINUS 100 mg COMPRIMIDOS DE LIBERACION PROLONGADA</t>
+          <t>MST CONTINUS 60 mg COMPRIMIDOS DE LIBERACION PROLONGADA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7511,22 +7516,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>58242</t>
+          <t>57900</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GELOCATIL GRIPE CON PSEUDOEFEDRINA COMPRIMIDOS</t>
+          <t>MST CONTINUS 100 mg COMPRIMIDOS DE LIBERACION PROLONGADA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Vemedia Pharma Hispania S.A.</t>
+          <t>Mundipharma Pharmaceuticals S.L.</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>01/10/1991</t>
+          <t>01/09/1988</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -7536,21 +7541,21 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>01/10/1991</t>
+          <t>01/09/1988</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>N02BE51</t>
+          <t>N02AA01</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>PARACETAMOL, PSEUDOEFEDRINA HIDROCLORURO, CLORFENAMINA MALEATO</t>
+          <t>MORFINA SULFATO</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -7564,12 +7569,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Sin Receta</t>
+          <t>Medicamento Sujeto A Prescripción Médica. Estupefacientes</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -7581,42 +7586,42 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>58967</t>
+          <t>58242</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ACYLINE 620 mg/380 mg/630 mg SUSPENSION ORAL</t>
+          <t>GELOCATIL GRIPE CON PSEUDOEFEDRINA COMPRIMIDOS</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Arafarma Group S.A.</t>
+          <t>Vemedia Pharma Hispania S.A.</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>31/03/2005</t>
+          <t>01/10/1991</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Suspenso</t>
+          <t>Autorizado</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>18/09/2025</t>
+          <t>01/10/1991</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>A02AD01</t>
+          <t>N02BE51</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>MAGNESIO HIDROXIDO, ALGELDRATO, ALUMINIO HIDROXIDO-MAGNESIO CARBONATO,COPRECIPITADO</t>
+          <t>PARACETAMOL, PSEUDOEFEDRINA HIDROCLORURO, CLORFENAMINA MALEATO</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -7624,7 +7629,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -7651,50 +7656,50 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>59166</t>
+          <t>58967</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DALSY 20 mg/ml SUSPENSION ORAL</t>
+          <t>ACYLINE 620 mg/380 mg/630 mg SUSPENSION ORAL</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Viatris Healthcare Limited</t>
+          <t>Arafarma Group S.A.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>01/12/1991</t>
+          <t>31/03/2005</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Autorizado</t>
+          <t>Suspenso</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>01/12/1991</t>
+          <t>18/09/2025</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>M01AE01</t>
+          <t>A02AD01</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>IBUPROFENO</t>
+          <t>MAGNESIO HIDROXIDO, ALGELDRATO, ALUMINIO HIDROXIDO-MAGNESIO CARBONATO,COPRECIPITADO</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -7721,22 +7726,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>59515</t>
+          <t>59166</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>AUGMENTINE 875 mg/125 mg COMPRIMIDOS RECUBIERTOS CON PELICULA</t>
+          <t>DALSY 20 mg/ml SUSPENSION ORAL</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Glaxosmithkline S.A.</t>
+          <t>Viatris Healthcare Limited</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>01/02/1993</t>
+          <t>01/12/1991</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -7746,21 +7751,21 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>01/02/1993</t>
+          <t>01/12/1991</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>J01CR02</t>
+          <t>M01AE01</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>AMOXICILINA TRIHIDRATO, CLAVULANATO POTASIO</t>
+          <t>IBUPROFENO</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -7774,7 +7779,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica</t>
+          <t>Sin Receta</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7791,12 +7796,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>59518</t>
+          <t>59515</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>AUGMENTINE 875 mg/125 mg POLVO PARA SUSPENSION ORAL EN SOBRES</t>
+          <t>AUGMENTINE 875 mg/125 mg COMPRIMIDOS RECUBIERTOS CON PELICULA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7826,7 +7831,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>AMOXICILINA TRIHIDRATO, CLAVULANICO ACIDO</t>
+          <t>AMOXICILINA TRIHIDRATO, CLAVULANATO POTASIO</t>
         </is>
       </c>
       <c r="I105" t="n">
@@ -7854,57 +7859,57 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>60054</t>
+          <t>59518</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DIANEAL PD4 GLUCOSA 2,27 % CON SISTEMA DE DESCONEXION INTEGRADO SOLUCION PARA DIALISIS PERITONEAL</t>
+          <t>AUGMENTINE 875 mg/125 mg POLVO PARA SUSPENSION ORAL EN SOBRES</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Vantive Health S.L.</t>
+          <t>Glaxosmithkline S.A.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>01/03/1994</t>
+          <t>01/02/1993</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Suspenso</t>
+          <t>Autorizado</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/02/1993</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>B05DB91</t>
+          <t>J01CR02</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>GLUCOSA MONOHIDRATO, GLUCOSA ANHIDRA, SODIO CLORURO, LACTATO SODIO, CALCIO CLORURO DIHIDRATO, MAGNESIO CLORURO HEXAHIDRATO</t>
+          <t>AMOXICILINA TRIHIDRATO, CLAVULANICO ACIDO</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7914,7 +7919,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Uso Hospitalario</t>
+          <t>Medicamento Sujeto A Prescripción Médica</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,57 +7929,57 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>60928</t>
+          <t>60054</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ENANTYUM 25 mg COMPRIMIDOS RECUBIERTOS CON PELICULA</t>
+          <t>DIANEAL PD4 GLUCOSA 2,27 % CON SISTEMA DE DESCONEXION INTEGRADO SOLUCION PARA DIALISIS PERITONEAL</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Laboratorios Menarini S.A.</t>
+          <t>Vantive Health S.L.</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>01/04/1996</t>
+          <t>01/03/1994</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Autorizado</t>
+          <t>Suspenso</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>01/04/1996</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>M01AE17</t>
+          <t>B05DB91</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>DEXKETOPROFENO TROMETAMOL</t>
+          <t>GLUCOSA MONOHIDRATO, GLUCOSA ANHIDRA, SODIO CLORURO, LACTATO SODIO, CALCIO CLORURO DIHIDRATO, MAGNESIO CLORURO HEXAHIDRATO</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7984,7 +7989,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica</t>
+          <t>Uso Hospitalario</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8001,42 +8006,42 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>62336</t>
+          <t>60928</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>AMOXICILINA PENSA 750 mg COMPRIMIDOS RECUBIERTOS EFG</t>
+          <t>ENANTYUM 25 mg COMPRIMIDOS RECUBIERTOS CON PELICULA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Pensa Pharma, S.A.U</t>
+          <t>Laboratorios Menarini S.A.</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>01/09/1999</t>
+          <t>01/04/1996</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Anulado</t>
+          <t>Autorizado</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>08/08/2022</t>
+          <t>01/04/1996</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>J01CA04</t>
+          <t>M01AE17</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>AMOXICILINA TRIHIDRATO</t>
+          <t>DEXKETOPROFENO TROMETAMOL</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -8044,7 +8049,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -8071,42 +8076,42 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>62685</t>
+          <t>62336</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ACICLOVIR SANDOZ 200 MG COMPRIMIDOS EFG</t>
+          <t>AMOXICILINA PENSA 750 mg COMPRIMIDOS RECUBIERTOS EFG</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sandoz Farmaceutica S.A.</t>
+          <t>Pensa Pharma, S.A.U</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>01/07/1999</t>
+          <t>01/09/1999</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Suspenso</t>
+          <t>Anulado</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2022</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>J05AB01</t>
+          <t>J01CA04</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>ACICLOVIR</t>
+          <t>AMOXICILINA TRIHIDRATO</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -8141,12 +8146,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>62686</t>
+          <t>62685</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ACICLOVIR SANDOZ 800 MG COMPRIMIDOS EFG</t>
+          <t>ACICLOVIR SANDOZ 200 MG COMPRIMIDOS EFG</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -8211,42 +8216,42 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>63429</t>
+          <t>62686</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>OMEPRAZOL TEVA-RIMAFAR 20 mg CAPSULAS DURAS GASTRORRESISTENTES EFG</t>
+          <t>ACICLOVIR SANDOZ 800 MG COMPRIMIDOS EFG</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Teva Pharma S.L.U.</t>
+          <t>Sandoz Farmaceutica S.A.</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>02/11/2000</t>
+          <t>01/07/1999</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Anulado</t>
+          <t>Suspenso</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>22/01/2024</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>A02BC01</t>
+          <t>J05AB01</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>OMEPRAZOL</t>
+          <t>ACICLOVIR</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -8281,42 +8286,42 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>63501</t>
+          <t>63429</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PARACETAMOL SUN 650 mg COMPRIMIDOS EFG</t>
+          <t>OMEPRAZOL TEVA-RIMAFAR 20 mg CAPSULAS DURAS GASTRORRESISTENTES EFG</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries (Europe) B.V.</t>
+          <t>Teva Pharma S.L.U.</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>28/11/2000</t>
+          <t>02/11/2000</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Autorizado</t>
+          <t>Anulado</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>28/11/2000</t>
+          <t>22/01/2024</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>N02BE01</t>
+          <t>A02BC01</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>PARACETAMOL</t>
+          <t>OMEPRAZOL</t>
         </is>
       </c>
       <c r="I112" t="n">
@@ -8324,7 +8329,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -8351,22 +8356,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>63990</t>
+          <t>63501</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DALSY 200 mg GRANULADO EFERVESCENTE</t>
+          <t>PARACETAMOL SUN 650 mg COMPRIMIDOS EFG</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Viatris Healthcare Limited</t>
+          <t>Sun Pharmaceutical Industries (Europe) B.V.</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>11/06/2001</t>
+          <t>28/11/2000</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8376,17 +8381,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>11/06/2001</t>
+          <t>28/11/2000</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>M01AE01</t>
+          <t>N02BE01</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>IBUPROFENO</t>
+          <t>PARACETAMOL</t>
         </is>
       </c>
       <c r="I113" t="n">
@@ -8404,7 +8409,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Sin Receta</t>
+          <t>Medicamento Sujeto A Prescripción Médica</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8421,22 +8426,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>64248</t>
+          <t>63990</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SIMVASTATINA KERN PHARMA 10 mg COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
+          <t>DALSY 200 mg GRANULADO EFERVESCENTE</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kern Pharma S.L.</t>
+          <t>Viatris Healthcare Limited</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>27/09/2001</t>
+          <t>11/06/2001</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8446,17 +8451,17 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>27/09/2001</t>
+          <t>11/06/2001</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>C10AA01</t>
+          <t>M01AE01</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>SIMVASTATINA</t>
+          <t>IBUPROFENO</t>
         </is>
       </c>
       <c r="I114" t="n">
@@ -8474,7 +8479,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica. Tratamiento De Larga Duración</t>
+          <t>Sin Receta</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8491,22 +8496,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>65517</t>
+          <t>64248</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>OMEPRAZOL SANDOZ FARMACEUTICA 10 MG CAPSULAS DURAS GASTRORRESISTENTES</t>
+          <t>SIMVASTATINA KERN PHARMA 10 mg COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sandoz Farmaceutica S.A.</t>
+          <t>Kern Pharma S.L.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>04/09/2003</t>
+          <t>27/09/2001</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8516,17 +8521,17 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>05/09/2003</t>
+          <t>27/09/2001</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>A02BC01</t>
+          <t>C10AA01</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>OMEPRAZOL</t>
+          <t>SIMVASTATINA</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -8544,7 +8549,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica</t>
+          <t>Medicamento Sujeto A Prescripción Médica. Tratamiento De Larga Duración</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8561,22 +8566,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>65920</t>
+          <t>65517</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>IBUPROFENO NORMON 20 mg/ml SUSPENSION ORAL EFG</t>
+          <t>OMEPRAZOL SANDOZ FARMACEUTICA 10 MG CAPSULAS DURAS GASTRORRESISTENTES</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Laboratorios Normon S.A.</t>
+          <t>Sandoz Farmaceutica S.A.</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>03/03/2004</t>
+          <t>04/09/2003</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8586,17 +8591,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>03/03/2004</t>
+          <t>05/09/2003</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>M01AE01</t>
+          <t>A02BC01</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>IBUPROFENO</t>
+          <t>OMEPRAZOL</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -8614,7 +8619,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Sin Receta</t>
+          <t>Medicamento Sujeto A Prescripción Médica</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8631,42 +8636,42 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>66387</t>
+          <t>65920</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PROMIXIN 1 MILLON DE UNIDADES INTERNACIONALES (UI), POLVO PARA SOLUCION PARA INHALACION POR NEBULIZADOR.</t>
+          <t>IBUPROFENO NORMON 20 mg/ml SUSPENSION ORAL EFG</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Zambon S.P.A.</t>
+          <t>Laboratorios Normon S.A.</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>28/09/2004</t>
+          <t>03/03/2004</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Suspenso</t>
+          <t>Autorizado</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>03/03/2004</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>J01XB01</t>
+          <t>M01AE01</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>COLISTIMETATO SODIO</t>
+          <t>IBUPROFENO</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -8674,7 +8679,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -8684,12 +8689,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Uso Hospitalario</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>Medicamentos para el aparato respiratorio administrados por vía inhalatoria</t>
+          <t>Sin Receta</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8706,50 +8706,50 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>66425</t>
+          <t>66387</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>AMOXICILINA/ACIDO CLAVULANICO NORMON 1.000 mg/200 mg POLVO PARA SOLUCION INYECTABLE Y PARA PERFUSION EFG</t>
+          <t>PROMIXIN 1 MILLON DE UNIDADES INTERNACIONALES (UI), POLVO PARA SOLUCION PARA INHALACION POR NEBULIZADOR.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Laboratorios Normon S.A.</t>
+          <t>Zambon S.P.A.</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>04/11/2004</t>
+          <t>28/09/2004</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Autorizado</t>
+          <t>Suspenso</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>04/11/2004</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>J01CR02</t>
+          <t>J01XB01</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>AMOXICILINA SODICA, CLAVULANATO POTASIO</t>
+          <t>COLISTIMETATO SODIO</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -8760,6 +8760,11 @@
       <c r="L118" t="inlineStr">
         <is>
           <t>Uso Hospitalario</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Medicamentos para el aparato respiratorio administrados por vía inhalatoria</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8776,22 +8781,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>66819</t>
+          <t>66425</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ENANTYUM 25 mg, GRANULADO PARA SOLUCION ORAL</t>
+          <t>AMOXICILINA/ACIDO CLAVULANICO NORMON 1.000 mg/200 mg POLVO PARA SOLUCION INYECTABLE Y PARA PERFUSION EFG</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Laboratorios Menarini S.A.</t>
+          <t>Laboratorios Normon S.A.</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>20/05/2005</t>
+          <t>04/11/2004</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -8801,21 +8806,21 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>20/05/2005</t>
+          <t>04/11/2004</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>M01AE17</t>
+          <t>J01CR02</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>DEXKETOPROFENO TROMETAMOL</t>
+          <t>AMOXICILINA SODICA, CLAVULANATO POTASIO</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -8829,7 +8834,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica</t>
+          <t>Uso Hospitalario</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8846,22 +8851,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>70569</t>
+          <t>66819</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>APIRETAL 250 mg COMPRIMIDOS BUCODISPERSABLES</t>
+          <t>ENANTYUM 25 mg, GRANULADO PARA SOLUCION ORAL</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Laboratorios Ern S.A.</t>
+          <t>Laboratorios Menarini S.A.</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>20/02/2009</t>
+          <t>20/05/2005</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -8871,17 +8876,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>20/02/2009</t>
+          <t>20/05/2005</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>N02BE01</t>
+          <t>M01AE17</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>PARACETAMOL</t>
+          <t>DEXKETOPROFENO TROMETAMOL</t>
         </is>
       </c>
       <c r="I120" t="n">
@@ -8899,7 +8904,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Sin Receta</t>
+          <t>Medicamento Sujeto A Prescripción Médica</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8916,12 +8921,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>70572</t>
+          <t>70569</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>APIRETAL 500 mg COMPRIMIDOS BUCODISPERSABLES</t>
+          <t>APIRETAL 250 mg COMPRIMIDOS BUCODISPERSABLES</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8986,22 +8991,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>71434</t>
+          <t>70572</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PARACETAMOL RATIO 1 g COMPRIMIDOS EFG</t>
+          <t>APIRETAL 500 mg COMPRIMIDOS BUCODISPERSABLES</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Teva Pharma S.L.U.</t>
+          <t>Laboratorios Ern S.A.</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>30/09/2009</t>
+          <t>20/02/2009</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -9011,7 +9016,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>30/09/2009</t>
+          <t>20/02/2009</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9039,7 +9044,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica</t>
+          <t>Sin Receta</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9056,22 +9061,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>72146</t>
+          <t>71371</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>OMEPRAZOL AUROVITAS SPAIN 40 mg CAPSULAS DURAS GASTRORRESISTENTES</t>
+          <t>MIBI INSTITUTE OF ATOMIC ENERGY 1 mg EQUIPO DE REACTIVOS PARA PREPARACION RADIOFARMACEUTICA EFG</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Aurovitas Spain, S.A.U.</t>
+          <t>Narodowe Centrum Badan Jadrowych</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>04/05/2010</t>
+          <t>11/09/2009</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -9081,17 +9086,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>04/05/2010</t>
+          <t>11/09/2009</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>A02BC01</t>
+          <t>V09GA01</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>OMEPRAZOL</t>
+          <t>[TETRAKIS (2-METOXI-2-METILPROPIL-1-ISOCIANURO) COBRE (I)], TETRAFLUOROBORATO DE</t>
         </is>
       </c>
       <c r="I123" t="n">
@@ -9109,7 +9114,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica</t>
+          <t>Uso Hospitalario</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9126,22 +9131,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>74969</t>
+          <t>71434</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>METFORMINA AUROVITAS 850 mg COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
+          <t>PARACETAMOL RATIO 1 g COMPRIMIDOS EFG</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Aurovitas Spain, S.A.U.</t>
+          <t>Teva Pharma S.L.U.</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>11/11/2011</t>
+          <t>30/09/2009</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -9151,17 +9156,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>11/11/2011</t>
+          <t>30/09/2009</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>A10BA02</t>
+          <t>N02BE01</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>METFORMINA HIDROCLORURO</t>
+          <t>PARACETAMOL</t>
         </is>
       </c>
       <c r="I124" t="n">
@@ -9196,22 +9201,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>76028</t>
+          <t>72146</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>APIRETAL 100 mg/ml SOLUCION ORAL SABOR CEREZA</t>
+          <t>OMEPRAZOL AUROVITAS SPAIN 40 mg CAPSULAS DURAS GASTRORRESISTENTES</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Laboratorios Ern S.A.</t>
+          <t>Aurovitas Spain, S.A.U.</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>12/06/2012</t>
+          <t>04/05/2010</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -9221,17 +9226,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>12/06/2012</t>
+          <t>04/05/2010</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>N02BE01</t>
+          <t>A02BC01</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>PARACETAMOL</t>
+          <t>OMEPRAZOL</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -9239,7 +9244,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -9249,7 +9254,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Sin Receta</t>
+          <t>Medicamento Sujeto A Prescripción Médica</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9266,42 +9271,42 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>76409</t>
+          <t>74969</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SIMVASTATINA PHARMA COMBIX 10 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
+          <t>METFORMINA AUROVITAS 850 mg COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Laboratorios Combix S.L.U.</t>
+          <t>Aurovitas Spain, S.A.U.</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>28/08/2012</t>
+          <t>11/11/2011</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Anulado</t>
+          <t>Autorizado</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>29/11/2024</t>
+          <t>11/11/2011</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>C10AA01</t>
+          <t>A10BA02</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>SIMVASTATINA</t>
+          <t>METFORMINA HIDROCLORURO</t>
         </is>
       </c>
       <c r="I126" t="n">
@@ -9309,7 +9314,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -9319,7 +9324,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica. Tratamiento De Larga Duración</t>
+          <t>Medicamento Sujeto A Prescripción Médica</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9336,22 +9341,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>76534</t>
+          <t>76028</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ATORVASTATINA SUN 20 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
+          <t>APIRETAL 100 mg/ml SOLUCION ORAL SABOR CEREZA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries (Europe) B.V.</t>
+          <t>Laboratorios Ern S.A.</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>27/09/2012</t>
+          <t>12/06/2012</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -9361,17 +9366,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>27/09/2012</t>
+          <t>12/06/2012</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>C10AA05</t>
+          <t>N02BE01</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>ATORVASTATINA CALCICA</t>
+          <t>PARACETAMOL</t>
         </is>
       </c>
       <c r="I127" t="n">
@@ -9379,7 +9384,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -9389,7 +9394,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica</t>
+          <t>Sin Receta</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9406,42 +9411,42 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>76536</t>
+          <t>76409</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ATORVASTATINA SUN 80 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
+          <t>SIMVASTATINA PHARMA COMBIX 10 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries (Europe) B.V.</t>
+          <t>Laboratorios Combix S.L.U.</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>27/09/2012</t>
+          <t>28/08/2012</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Autorizado</t>
+          <t>Anulado</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>27/09/2012</t>
+          <t>29/11/2024</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>C10AA05</t>
+          <t>C10AA01</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>ATORVASTATINA CALCICA</t>
+          <t>SIMVASTATINA</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -9449,7 +9454,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -9459,7 +9464,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica</t>
+          <t>Medicamento Sujeto A Prescripción Médica. Tratamiento De Larga Duración</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9476,22 +9481,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>78433</t>
+          <t>76534</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TERMALGIN RESFRIADO 500 MG/30 MG POLVO PARA SOLUCION ORAL</t>
+          <t>ATORVASTATINA SUN 20 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Haleon Spain S.A.</t>
+          <t>Sun Pharmaceutical Industries (Europe) B.V.</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>03/02/2014</t>
+          <t>27/09/2012</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -9501,21 +9506,21 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>18/05/2016</t>
+          <t>27/09/2012</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>R05X_</t>
+          <t>C10AA05</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>PARACETAMOL, PSEUDOEFEDRINA HIDROCLORURO</t>
+          <t>ATORVASTATINA CALCICA</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -9529,7 +9534,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Sin Receta</t>
+          <t>Medicamento Sujeto A Prescripción Médica</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9546,22 +9551,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>78705</t>
+          <t>76536</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ENANTYUM 25 MG CAPSULAS DURAS</t>
+          <t>ATORVASTATINA SUN 80 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Laboratorios Menarini S.A.</t>
+          <t>Sun Pharmaceutical Industries (Europe) B.V.</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>29/04/2014</t>
+          <t>27/09/2012</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -9571,17 +9576,17 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>29/04/2014</t>
+          <t>27/09/2012</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>M01AE17</t>
+          <t>C10AA05</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>DEXKETOPROFENO TROMETAMOL</t>
+          <t>ATORVASTATINA CALCICA</t>
         </is>
       </c>
       <c r="I130" t="n">
@@ -9616,22 +9621,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>78868</t>
+          <t>78433</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PARACETAMOL PENSAVITAL 1 G COMPRIMIDOS EFERVESCENTES EFG</t>
+          <t>TERMALGIN RESFRIADO 500 MG/30 MG POLVO PARA SOLUCION ORAL</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Towa Pharmaceutical S.A.</t>
+          <t>Haleon Spain S.A.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>30/06/2014</t>
+          <t>03/02/2014</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -9641,25 +9646,25 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>30/06/2014</t>
+          <t>18/05/2016</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>N02BE01</t>
+          <t>R05X_</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>PARACETAMOL</t>
+          <t>PARACETAMOL, PSEUDOEFEDRINA HIDROCLORURO</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -9686,22 +9691,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>81482</t>
+          <t>78705</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>AUGMENTINE 500 MG/125 MG COMPRIMIDOS RECUBIERTOS CON PELÍCULA.</t>
+          <t>ENANTYUM 25 MG CAPSULAS DURAS</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Glaxosmithkline S.A.</t>
+          <t>Laboratorios Menarini S.A.</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>01/12/2016</t>
+          <t>29/04/2014</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -9711,21 +9716,21 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>13/08/2017</t>
+          <t>29/04/2014</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>J01CR02</t>
+          <t>M01AE17</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>AMOXICILINA TRIHIDRATO, CLAVULANATO POTASIO</t>
+          <t>DEXKETOPROFENO TROMETAMOL</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -9756,22 +9761,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>81972</t>
+          <t>78868</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GELOCATIL PLUS 500 MG/65 MG COMPRIMIDOS RECUBIERTOS CON PELICULA</t>
+          <t>PARACETAMOL PENSAVITAL 1 G COMPRIMIDOS EFERVESCENTES EFG</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Vemedia Pharma Hispania S.A.</t>
+          <t>Towa Pharmaceutical S.A.</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>21/04/2017</t>
+          <t>30/06/2014</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -9781,25 +9786,25 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>22/04/2017</t>
+          <t>30/06/2014</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>N02BE51</t>
+          <t>N02BE01</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>PARACETAMOL, CAFEINA</t>
+          <t>PARACETAMOL</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -9826,22 +9831,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>82050</t>
+          <t>81482</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TERMALGIN GRIPE 650 MG/15,58 MG/4 MG GRANULADO PARA SOLUCION ORAL</t>
+          <t>AUGMENTINE 500 MG/125 MG COMPRIMIDOS RECUBIERTOS CON PELÍCULA.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Haleon Spain S.A.</t>
+          <t>Glaxosmithkline S.A.</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>22/05/2017</t>
+          <t>01/12/2016</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -9851,21 +9856,21 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>23/05/2017</t>
+          <t>13/08/2017</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>N02BE51</t>
+          <t>J01CR02</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>PARACETAMOL, CLORFENAMINA MALEATO, FENILEFRINA BITARTRATO</t>
+          <t>AMOXICILINA TRIHIDRATO, CLAVULANATO POTASIO</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -9879,7 +9884,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Sin Receta</t>
+          <t>Medicamento Sujeto A Prescripción Médica</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9896,22 +9901,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>82814</t>
+          <t>81972</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>IBUPROFENO ALTER GENERICOS 600 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
+          <t>GELOCATIL PLUS 500 MG/65 MG COMPRIMIDOS RECUBIERTOS CON PELICULA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Laboratorios Alter S.A.</t>
+          <t>Vemedia Pharma Hispania S.A.</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>22/01/2018</t>
+          <t>21/04/2017</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -9921,21 +9926,21 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>23/01/2018</t>
+          <t>22/04/2017</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>M01AE01</t>
+          <t>N02BE51</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>IBUPROFENO</t>
+          <t>PARACETAMOL, CAFEINA</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -9949,7 +9954,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica</t>
+          <t>Sin Receta</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9966,22 +9971,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>83166</t>
+          <t>82050</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>METFORMINA ALMUS PHARMA 1.000 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
+          <t>TERMALGIN GRIPE 650 MG/15,58 MG/4 MG GRANULADO PARA SOLUCION ORAL</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Almus Farmaceutica S.A.U.</t>
+          <t>Haleon Spain S.A.</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>31/05/2018</t>
+          <t>22/05/2017</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -9991,21 +9996,21 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>01/06/2018</t>
+          <t>23/05/2017</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>A10BA02</t>
+          <t>N02BE51</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>METFORMINA HIDROCLORURO</t>
+          <t>PARACETAMOL, CLORFENAMINA MALEATO, FENILEFRINA BITARTRATO</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -10019,7 +10024,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica</t>
+          <t>Sin Receta</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10036,50 +10041,50 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>85135</t>
+          <t>82814</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>OLMESARTAN/AMLODIPINO/HIDROCLOROTIAZIDA STADAGEN 40 MG/5 MG/25 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
+          <t>IBUPROFENO ALTER GENERICOS 600 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Laboratorio Stada S.L.</t>
+          <t>Laboratorios Alter S.A.</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>08/06/2020</t>
+          <t>22/01/2018</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Anulado</t>
+          <t>Autorizado</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>22/11/2024</t>
+          <t>23/01/2018</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>C09DX03</t>
+          <t>M01AE01</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>HIDROCLOROTIAZIDA, AMLODIPINO BESILATO, OLMESARTAN MEDOXOMILO</t>
+          <t>IBUPROFENO</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -10106,50 +10111,50 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>85150</t>
+          <t>83166</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>OLMESARTAN/AMLODIPINO/HIDROCLOROTIAZIDA EDEST 40MG/10MG/25MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
+          <t>METFORMINA ALMUS PHARMA 1.000 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Intas Third Party Sales 2005 S.L.</t>
+          <t>Almus Farmaceutica S.A.U.</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>10/06/2020</t>
+          <t>31/05/2018</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Anulado</t>
+          <t>Autorizado</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>01/06/2018</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>C09DX03</t>
+          <t>A10BA02</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>HIDROCLOROTIAZIDA, AMLODIPINO BESILATO, OLMESARTAN MEDOXOMILO</t>
+          <t>METFORMINA HIDROCLORURO</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -10176,22 +10181,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>85151</t>
+          <t>85135</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>OLMESARTAN/AMLODIPINO/HIDROCLOROTIAZIDA EDEST 40MG/10MG/12.5MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
+          <t>OLMESARTAN/AMLODIPINO/HIDROCLOROTIAZIDA STADAGEN 40 MG/5 MG/25 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Intas Third Party Sales 2005 S.L.</t>
+          <t>Laboratorio Stada S.L.</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>10/06/2020</t>
+          <t>08/06/2020</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -10201,7 +10206,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>19/06/2025</t>
+          <t>22/11/2024</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10246,50 +10251,50 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>85940</t>
+          <t>85150</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SIMVASTATINA VIATRIS 20 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
+          <t>OLMESARTAN/AMLODIPINO/HIDROCLOROTIAZIDA EDEST 40MG/10MG/25MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Viatris Limited</t>
+          <t>Intas Third Party Sales 2005 S.L.</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>23/04/2021</t>
+          <t>10/06/2020</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Autorizado</t>
+          <t>Anulado</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>24/04/2021</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>C10AA01</t>
+          <t>C09DX03</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>SIMVASTATINA</t>
+          <t>HIDROCLOROTIAZIDA, AMLODIPINO BESILATO, OLMESARTAN MEDOXOMILO</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -10299,7 +10304,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica. Tratamiento De Larga Duración</t>
+          <t>Medicamento Sujeto A Prescripción Médica</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10316,46 +10321,46 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>86703</t>
+          <t>85151</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ATORVASTATINA MABO-FARMA 10 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
+          <t>OLMESARTAN/AMLODIPINO/HIDROCLOROTIAZIDA EDEST 40MG/10MG/12.5MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Mabo Farma S.A.</t>
+          <t>Intas Third Party Sales 2005 S.L.</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>28/03/2022</t>
+          <t>10/06/2020</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Autorizado</t>
+          <t>Anulado</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>29/03/2022</t>
+          <t>19/06/2025</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>C10AA05</t>
+          <t>C09DX03</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>ATORVASTATINA CALCICA TRIHIDRATO</t>
+          <t>HIDROCLOROTIAZIDA, AMLODIPINO BESILATO, OLMESARTAN MEDOXOMILO</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -10386,22 +10391,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>89110</t>
+          <t>85245</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>METFORMINA PHARMA COMBIX 1.000 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
+          <t>NEVIRAPINA TARBIS FARMA 400 MG COMPRIMIDOS DE LIBERACION PROLONGADA EFG</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Laboratorios Combix S.L.U.</t>
+          <t>Tarbis Farma S.L.</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>31/10/2023</t>
+          <t>13/07/2020</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -10411,17 +10416,17 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>01/11/2023</t>
+          <t>14/07/2020</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>A10BA02</t>
+          <t>J05AG01</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>METFORMINA HIDROCLORURO</t>
+          <t>NEVIRAPINA, ANHIDRA</t>
         </is>
       </c>
       <c r="I142" t="n">
@@ -10439,7 +10444,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Medicamento Sujeto A Prescripción Médica</t>
+          <t>Diagnóstico Hospitalario</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10456,22 +10461,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>90651</t>
+          <t>85940</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DALSYDOL RAPID 400 MG CAPSULAS BLANDAS</t>
+          <t>SIMVASTATINA VIATRIS 20 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Viatris Healthcare Limited</t>
+          <t>Viatris Limited</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>23/04/2021</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -10481,17 +10486,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>08/10/2025</t>
+          <t>24/04/2021</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>M01AE01</t>
+          <t>C10AA01</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>IBUPROFENO</t>
+          <t>SIMVASTATINA</t>
         </is>
       </c>
       <c r="I143" t="n">
@@ -10509,15 +10514,225 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
+          <t>Medicamento Sujeto A Prescripción Médica. Tratamiento De Larga Duración</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>86703</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ATORVASTATINA MABO-FARMA 10 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Mabo Farma S.A.</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>28/03/2022</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Autorizado</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>29/03/2022</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>C10AA05</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>ATORVASTATINA CALCICA TRIHIDRATO</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>1</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Medicamento Sujeto A Prescripción Médica</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>89110</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>METFORMINA PHARMA COMBIX 1.000 MG COMPRIMIDOS RECUBIERTOS CON PELICULA EFG</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Laboratorios Combix S.L.U.</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>31/10/2023</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Autorizado</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>01/11/2023</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>A10BA02</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>METFORMINA HIDROCLORURO</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>1</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Medicamento Sujeto A Prescripción Médica</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>90651</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>DALSYDOL RAPID 400 MG CAPSULAS BLANDAS</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Viatris Healthcare Limited</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Autorizado</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>08/10/2025</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>M01AE01</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>IBUPROFENO</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>1</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
           <t>Sin Receta</t>
         </is>
       </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O143" t="inlineStr">
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
